--- a/PlanesEstudio/Plan_LISTI_2023.xlsx
+++ b/PlanesEstudio/Plan_LISTI_2023.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.282054" customWidth="1" style="5" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="8.424911" customWidth="1" style="5" min="3" max="3"/>
     <col width="8.710625" customWidth="1" style="5" min="4" max="4"/>
     <col width="34.424911" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.996339000000001" customWidth="1" style="5" min="6" max="6"/>
+    <col width="26" customWidth="1" style="5" min="6" max="6"/>
     <col width="20" customWidth="1" style="10" min="7" max="7"/>
     <col width="18" customWidth="1" style="10" min="8" max="8"/>
   </cols>
@@ -561,7 +561,7 @@
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -587,7 +587,7 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -613,7 +613,7 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -639,7 +639,7 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -665,7 +665,7 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -691,7 +691,7 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -803,7 +803,7 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -829,7 +829,7 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -937,7 +937,7 @@
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -1811,14 +1811,13 @@
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
     </row>
-    <row r="50"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="" error="" promptTitle="" prompt="" type="list" errorStyle="stop" operator="between">
       <formula1>"Normal,Optativa,AFEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="" error="" promptTitle="" prompt="" type="list" errorStyle="stop" operator="between">
-      <formula1>"General,Básica,Disciplinar,Terminal"</formula1>
+      <formula1>"AFBG,Iniciación a la disciplina,Disciplinar,Terminal"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -2053,7 +2052,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Area (opcional): General, Básica, Disciplinar o Terminal. Define el color de la tarjeta; vacía = gris.</t>
+          <t xml:space="preserve">  • Area (opcional): AFBG, Iniciación a la disciplina, Disciplinar o Terminal. Define el color de la tarjeta; vacía = gris.</t>
         </is>
       </c>
     </row>
